--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488031_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488031_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3057</v>
+        <v>6.2058</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2485</v>
+        <v>4.2699</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0573</v>
+        <v>1.9359</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4213</v>
+        <v>2.7299</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6797</v>
+        <v>3.7859</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2584</v>
+        <v>-1.056</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8427</v>
+        <v>3.6015</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7221</v>
+        <v>3.7467</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1205</v>
+        <v>-0.1451</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4214</v>
+        <v>-0.8716</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0424</v>
+        <v>0.0392</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.379</v>
+        <v>-0.9109</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3801</v>
+        <v>-1.1564</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9708</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.1856</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0663</v>
+        <v>4.6323</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3329</v>
+        <v>3.6213</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2666</v>
+        <v>1.0109</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2595</v>
+        <v>5.3296</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9413</v>
+        <v>4.4127</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3182</v>
+        <v>0.9169</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7299</v>
+        <v>4.4213</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7859</v>
+        <v>4.6797</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.056</v>
+        <v>-0.2584</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6015</v>
+        <v>4.8427</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7467</v>
+        <v>4.7221</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1451</v>
+        <v>0.1205</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8716</v>
+        <v>-0.4214</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0392</v>
+        <v>-0.0424</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9109</v>
+        <v>-0.379</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.1027</v>
+        <v>-0.3562</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2993</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8034</v>
+        <v>0.4155</v>
       </c>
       <c r="V3" t="n">
-        <v>4.6323</v>
+        <v>1.0663</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6213</v>
+        <v>1.3329</v>
       </c>
       <c r="X3" t="n">
-        <v>1.0109</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6141</v>
+        <v>3.0683</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5138</v>
+        <v>2.333</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1003</v>
+        <v>0.7353</v>
       </c>
       <c r="G4" t="n">
         <v>4.0595</v>
@@ -766,13 +766,13 @@
         <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5458</v>
+        <v>-0.0001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0586</v>
+        <v>-0.2394</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6044</v>
+        <v>0.2393</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2655</v>
+        <v>2.4304</v>
       </c>
       <c r="E5" t="n">
-        <v>0.996</v>
+        <v>2.343</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2695</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7436</v>
+        <v>1.6381</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5202</v>
+        <v>4.437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7766</v>
+        <v>-2.799</v>
       </c>
       <c r="J5" t="n">
-        <v>2.227</v>
+        <v>2.0516</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4888</v>
+        <v>4.6074</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2618</v>
+        <v>-2.5558</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4834</v>
+        <v>-0.4135</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0314</v>
+        <v>-0.1704</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5148</v>
+        <v>-0.2431</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1411</v>
+        <v>-0.3663</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5064</v>
+        <v>-0.7441</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3654</v>
+        <v>0.3778</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2666</v>
+        <v>1.9515</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>3.0178</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.1367</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9126</v>
+        <v>0.9795</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08740000000000001</v>
+        <v>1.1572</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6381</v>
+        <v>1.7436</v>
       </c>
       <c r="H6" t="n">
-        <v>4.437</v>
+        <v>2.5202</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.799</v>
+        <v>-0.7766</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0516</v>
+        <v>2.227</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6074</v>
+        <v>2.4888</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.5558</v>
+        <v>-0.2618</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4135</v>
+        <v>-0.4834</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1704</v>
+        <v>0.0314</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2431</v>
+        <v>-0.5148</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7967</v>
+        <v>-0.2699</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1745</v>
+        <v>-0.523</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3778</v>
+        <v>0.253</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9515</v>
+        <v>0.2666</v>
       </c>
       <c r="W6" t="n">
-        <v>3.0178</v>
+        <v>0.2666</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0663</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2717</v>
+        <v>0.4359</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0624</v>
+        <v>0.1019</v>
       </c>
       <c r="F7" t="n">
         <v>0.334</v>
@@ -1000,10 +1000,10 @@
         <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0624</v>
+        <v>0.1019</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0624</v>
+        <v>0.1019</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.162</v>
+        <v>0.3544</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1248</v>
+        <v>0.0395</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2868</v>
+        <v>0.3149</v>
       </c>
       <c r="G8" t="n">
         <v>0.2057</v>
@@ -1078,13 +1078,13 @@
         <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2419</v>
+        <v>-0.0496</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1248</v>
+        <v>0.0395</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3178</v>
+        <v>-0.115</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5546</v>
+        <v>0.617</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8723</v>
+        <v>-0.7319</v>
       </c>
       <c r="G9" t="n">
         <v>0.0645</v>
@@ -1156,13 +1156,13 @@
         <v>0.9911</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1068</v>
+        <v>-0.904</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4881</v>
+        <v>-0.4257</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6186</v>
+        <v>-0.4782</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2666</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.964</v>
+        <v>-5.3133</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0996</v>
+        <v>-3.2804</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8645</v>
+        <v>-2.0329</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3802</v>
@@ -1234,13 +1234,13 @@
         <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3767</v>
+        <v>-0.726</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.433</v>
+        <v>-0.6138</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0563</v>
+        <v>-0.1122</v>
       </c>
       <c r="V10" t="n">
         <v>-3.0178</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>13.5967</v>
+        <v>14.5328</v>
       </c>
       <c r="E11" t="n">
-        <v>10.88</v>
+        <v>11.8161</v>
       </c>
       <c r="F11" t="n">
-        <v>2.716700000000001</v>
+        <v>2.716800000000001</v>
       </c>
       <c r="G11" t="n">
         <v>14.6182</v>
@@ -1312,13 +1312,13 @@
         <v>9.911000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.662599999999999</v>
+        <v>-3.7266</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.0831</v>
+        <v>-4.1471</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4207</v>
+        <v>0.4206</v>
       </c>
       <c r="V11" t="n">
         <v>4.632300000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.5134</v>
+        <v>3.4901</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1489</v>
+        <v>3.1302</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3645</v>
+        <v>0.3599</v>
       </c>
       <c r="G12" t="n">
         <v>1.3926</v>
@@ -1390,13 +1390,13 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9731</v>
+        <v>0.9498</v>
       </c>
       <c r="T12" t="n">
-        <v>1.351</v>
+        <v>0.3323</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6221</v>
+        <v>0.6175</v>
       </c>
       <c r="V12" t="n">
         <v>1.5441</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0543</v>
+        <v>0.1873</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1639</v>
+        <v>0.7569</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2182</v>
+        <v>-0.5696</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.0566</v>
+        <v>0.8677</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.3174</v>
+        <v>-0.0163</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2608</v>
+        <v>0.8839</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.251</v>
+        <v>0.9899</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.5004</v>
+        <v>0.3834</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2494</v>
+        <v>0.6066</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8056</v>
+        <v>-0.1223</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.817</v>
+        <v>-0.3996</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0114</v>
+        <v>0.2774</v>
       </c>
       <c r="P15" t="n">
         <v>0.3964</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2517</v>
+        <v>0.1303</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6154</v>
+        <v>-0.233</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6363</v>
+        <v>0.3634</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4627</v>
+        <v>-1.2071</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4627</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>D. RUBIO MIRAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0399</v>
+        <v>-0.5686</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5532</v>
+        <v>0.5325</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5931</v>
+        <v>-1.1011</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8677</v>
+        <v>-2.7007</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0163</v>
+        <v>-4.9258</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8839</v>
+        <v>2.2251</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9899</v>
+        <v>1.1701</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3834</v>
+        <v>-0.7662</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6066</v>
+        <v>1.9363</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1223</v>
+        <v>-3.8708</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3996</v>
+        <v>-4.1596</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2774</v>
+        <v>0.2888</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3964</v>
+        <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0969</v>
+        <v>0.6673</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4368</v>
+        <v>-0.1796</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3398</v>
+        <v>0.8469</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2071</v>
+        <v>0.8701</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2071</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5463</v>
+        <v>-1.4298</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0164</v>
+        <v>-1.4227</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5627</v>
+        <v>-0.0071</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9499</v>
+        <v>-1.7015</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2726</v>
+        <v>-1.7416</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6773</v>
+        <v>0.0402</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2358</v>
+        <v>-1.2979</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7944</v>
+        <v>-1.3381</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5586</v>
+        <v>0.0402</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1857</v>
+        <v>-0.4036</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.067</v>
+        <v>-0.4036</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1187</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0.3964</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4214</v>
+        <v>-0.1248</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9788</v>
+        <v>-0.1248</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4426</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4298</v>
+        <v>-1.5821</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4227</v>
+        <v>-1.1826</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0071</v>
+        <v>-0.3995</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7015</v>
+        <v>-4.0566</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7416</v>
+        <v>-5.3174</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0402</v>
+        <v>1.2608</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2979</v>
+        <v>-1.251</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3381</v>
+        <v>-2.5004</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>1.2494</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4036</v>
+        <v>-2.8056</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4036</v>
+        <v>-2.817</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="P18" t="n">
         <v>0.3964</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1248</v>
+        <v>1.6153</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1248</v>
+        <v>0.5967</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.0185</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.4627</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.4627</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. RUBIO MIRAS</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8844</v>
+        <v>-1.7452</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2824</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.602</v>
+        <v>-2.5392</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7007</v>
+        <v>-0.9499</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.9258</v>
+        <v>-0.2726</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2251</v>
+        <v>-0.6773</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1701</v>
+        <v>0.2358</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7662</v>
+        <v>0.7944</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9363</v>
+        <v>-0.5586</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.8708</v>
+        <v>-1.1857</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.1596</v>
+        <v>-1.067</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2888</v>
+        <v>-0.1187</v>
       </c>
       <c r="P19" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.1982</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.5947</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9911</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.5858</v>
-      </c>
       <c r="S19" t="n">
-        <v>-0.6485</v>
+        <v>1.2224</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9946</v>
+        <v>0.7564</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3461</v>
+        <v>0.4661</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8701</v>
+        <v>-2.4142</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.337</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8459</v>
+        <v>-1.7959</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9536</v>
+        <v>-1.2405</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8924</v>
+        <v>-0.5554</v>
       </c>
       <c r="G20" t="n">
         <v>-3.335</v>
@@ -2014,13 +2014,13 @@
         <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0967</v>
+        <v>-0.0467</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4131</v>
+        <v>-0.7</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3163</v>
+        <v>0.6533</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PEREZ</t>
+          <t>A. CONTRERAS RUBINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.7832</v>
+        <v>-6.0082</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4572</v>
+        <v>-2.7534</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.326</v>
+        <v>-3.2549</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9779</v>
+        <v>-4.8755</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7623</v>
+        <v>-5.2122</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7844</v>
+        <v>0.3367</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5553</v>
+        <v>-1.6799</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4672</v>
+        <v>-1.7278</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0881</v>
+        <v>0.048</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.5332</v>
+        <v>-3.1956</v>
       </c>
       <c r="N21" t="n">
-        <v>-4.2295</v>
+        <v>-3.4844</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6962</v>
+        <v>0.2888</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.3698</v>
+        <v>0.9911</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.1538</v>
+        <v>-1.1893</v>
       </c>
       <c r="R21" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0322</v>
+        <v>0.3608</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8587</v>
+        <v>-0.4173</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8265</v>
+        <v>0.7781</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4033</v>
+        <v>-2.4846</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4033</v>
+        <v>-3.0178</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBINO</t>
+          <t>A. GONZALEZ PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.3534</v>
+        <v>-6.1837</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8739</v>
+        <v>-4.0498</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4795</v>
+        <v>-2.134</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.8755</v>
+        <v>-1.9779</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.2122</v>
+        <v>-2.7623</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3367</v>
+        <v>0.7844</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6799</v>
+        <v>1.5553</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7278</v>
+        <v>1.4672</v>
       </c>
       <c r="L22" t="n">
-        <v>0.048</v>
+        <v>0.0881</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1956</v>
+        <v>-3.5332</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.4844</v>
+        <v>-4.2295</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2888</v>
+        <v>0.6962</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9911</v>
+        <v>-3.3698</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1893</v>
+        <v>-5.1538</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9844000000000001</v>
+        <v>0.5673</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5379</v>
+        <v>-0.4513</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5534</v>
+        <v>1.0185</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4846</v>
+        <v>-1.4033</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.0178</v>
+        <v>-1.4033</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-13.5965</v>
+        <v>-12.9174</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.716500000000001</v>
+        <v>-2.7168</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.8801</v>
+        <v>-10.2009</v>
       </c>
       <c r="G23" t="n">
         <v>-14.6181</v>
@@ -2224,7 +2224,7 @@
         <v>4.008599999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1335</v>
+        <v>0.1335000000000004</v>
       </c>
       <c r="L23" t="n">
         <v>3.8753</v>
@@ -2239,25 +2239,25 @@
         <v>2.1515</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9909999999999998</v>
+        <v>0.9910000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-9.911</v>
+        <v>-9.911000000000001</v>
       </c>
       <c r="R23" t="n">
         <v>10.9023</v>
       </c>
       <c r="S23" t="n">
-        <v>4.6627</v>
+        <v>5.3417</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4206999999999999</v>
+        <v>-0.4206</v>
       </c>
       <c r="U23" t="n">
-        <v>5.0831</v>
+        <v>5.7623</v>
       </c>
       <c r="V23" t="n">
-        <v>-4.632300000000001</v>
+        <v>-4.6323</v>
       </c>
       <c r="W23" t="n">
         <v>3.6062</v>
